--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.248824</v>
+        <v>0.399179</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121744</v>
+        <v>0.213987</v>
       </c>
       <c r="E4" t="n">
-        <v>0.29084</v>
+        <v>0.8072009999999999</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.287072</v>
+        <v>0.6165079999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.146569</v>
+        <v>0.312598</v>
       </c>
       <c r="E5" t="n">
-        <v>0.385642</v>
+        <v>0.964425</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.563588</v>
+        <v>0.766636</v>
       </c>
       <c r="D2" t="n">
-        <v>0.334179</v>
+        <v>0.476308</v>
       </c>
       <c r="E2" t="n">
-        <v>0.770825</v>
+        <v>0.91018</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.717422</v>
+        <v>0.864212</v>
       </c>
       <c r="D3" t="n">
-        <v>0.439594</v>
+        <v>0.648749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.826489</v>
+        <v>1.111115</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.399179</v>
+        <v>0.421855</v>
       </c>
       <c r="D4" t="n">
-        <v>0.213987</v>
+        <v>0.279901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8072009999999999</v>
+        <v>0.6951349999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6165079999999999</v>
+        <v>0.675715</v>
       </c>
       <c r="D5" t="n">
-        <v>0.312598</v>
+        <v>0.366137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.964425</v>
+        <v>1.109808</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.421855</v>
+        <v>0.386567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.279901</v>
+        <v>0.277274</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6951349999999999</v>
+        <v>0.698112</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.675715</v>
+        <v>0.679728</v>
       </c>
       <c r="D5" t="n">
-        <v>0.366137</v>
+        <v>0.355007</v>
       </c>
       <c r="E5" t="n">
-        <v>1.109808</v>
+        <v>1.058084</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.766636</v>
+        <v>0.766024</v>
       </c>
       <c r="D2" t="n">
         <v>0.476308</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.864212</v>
+        <v>0.865683</v>
       </c>
       <c r="D3" t="n">
-        <v>0.648749</v>
+        <v>0.63929</v>
       </c>
       <c r="E3" t="n">
-        <v>1.111115</v>
+        <v>1.126038</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.386567</v>
+        <v>0.385686</v>
       </c>
       <c r="D4" t="n">
-        <v>0.277274</v>
+        <v>0.28073</v>
       </c>
       <c r="E4" t="n">
-        <v>0.698112</v>
+        <v>0.6829539999999999</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.679728</v>
+        <v>0.600541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.355007</v>
+        <v>0.357343</v>
       </c>
       <c r="E5" t="n">
-        <v>1.058084</v>
+        <v>1.047587</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.385686</v>
+        <v>0.38559</v>
       </c>
       <c r="D4" t="n">
-        <v>0.28073</v>
+        <v>0.28066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6829539999999999</v>
+        <v>0.684151</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.600541</v>
+        <v>0.601285</v>
       </c>
       <c r="D5" t="n">
-        <v>0.357343</v>
+        <v>0.357725</v>
       </c>
       <c r="E5" t="n">
-        <v>1.047587</v>
+        <v>1.049405</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
